--- a/artfynd/A 12894-2025 artfynd.xlsx
+++ b/artfynd/A 12894-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123874759</v>
+        <v>123874704</v>
       </c>
       <c r="B2" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -708,7 +708,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -719,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586475</v>
+        <v>586387</v>
       </c>
       <c r="R2" t="n">
-        <v>6931222</v>
+        <v>6931007</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -765,6 +769,11 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flertalet knärötter, flera små på gång. I en grop.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123874676</v>
+        <v>123874788</v>
       </c>
       <c r="B3" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586387</v>
+        <v>586490</v>
       </c>
       <c r="R3" t="n">
-        <v>6931018</v>
+        <v>6931210</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -886,7 +895,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Vid granlåga.</t>
+          <t>Hundratals.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123874718</v>
+        <v>123874759</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -958,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586339</v>
+        <v>586475</v>
       </c>
       <c r="R4" t="n">
-        <v>6931134</v>
+        <v>6931222</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1004,11 +1013,6 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>I slänten ner mot fuktig mark.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,7 +1043,7 @@
         <v>123874645</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1158,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123874615</v>
+        <v>123874739</v>
       </c>
       <c r="B6" t="n">
-        <v>90988</v>
+        <v>79869</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,21 +1178,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1201,13 +1205,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586434</v>
+        <v>586451</v>
       </c>
       <c r="R6" t="n">
-        <v>6931019</v>
+        <v>6931253</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1251,7 +1255,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Granlåga, rotvälta.</t>
+          <t>På avbruten sälg.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,10 +1283,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123874739</v>
+        <v>123874718</v>
       </c>
       <c r="B7" t="n">
-        <v>79867</v>
+        <v>98504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,30 +1295,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1322,10 +1327,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586451</v>
+        <v>586339</v>
       </c>
       <c r="R7" t="n">
-        <v>6931253</v>
+        <v>6931134</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1372,7 +1377,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På avbruten sälg.</t>
+          <t>I slänten ner mot fuktig mark.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1400,10 +1405,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123874704</v>
+        <v>123874615</v>
       </c>
       <c r="B8" t="n">
-        <v>98502</v>
+        <v>90990</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,35 +1417,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1448,13 +1448,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586387</v>
+        <v>586434</v>
       </c>
       <c r="R8" t="n">
-        <v>6931007</v>
+        <v>6931019</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Flertalet knärötter, flera små på gång. I en grop.</t>
+          <t>Granlåga, rotvälta.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1526,10 +1526,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123874788</v>
+        <v>123874676</v>
       </c>
       <c r="B9" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586490</v>
+        <v>586387</v>
       </c>
       <c r="R9" t="n">
-        <v>6931210</v>
+        <v>6931018</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Hundratals.</t>
+          <t>Vid granlåga.</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 12894-2025 artfynd.xlsx
+++ b/artfynd/A 12894-2025 artfynd.xlsx
@@ -1162,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123874739</v>
+        <v>123874718</v>
       </c>
       <c r="B6" t="n">
-        <v>79869</v>
+        <v>98504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,30 +1174,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1205,10 +1206,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586451</v>
+        <v>586339</v>
       </c>
       <c r="R6" t="n">
-        <v>6931253</v>
+        <v>6931134</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1255,7 +1256,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På avbruten sälg.</t>
+          <t>I slänten ner mot fuktig mark.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1283,10 +1284,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123874718</v>
+        <v>123874739</v>
       </c>
       <c r="B7" t="n">
-        <v>98504</v>
+        <v>79869</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1295,31 +1296,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586339</v>
+        <v>586451</v>
       </c>
       <c r="R7" t="n">
-        <v>6931134</v>
+        <v>6931253</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>I slänten ner mot fuktig mark.</t>
+          <t>På avbruten sälg.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 12894-2025 artfynd.xlsx
+++ b/artfynd/A 12894-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123874704</v>
+        <v>123874645</v>
       </c>
       <c r="B2" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -708,11 +708,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -723,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586387</v>
+        <v>586409</v>
       </c>
       <c r="R2" t="n">
-        <v>6931007</v>
+        <v>6931021</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -773,7 +769,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Flertalet knärötter, flera små på gång. I en grop.</t>
+          <t>På liten kulle nära stor asp.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123874788</v>
+        <v>123874704</v>
       </c>
       <c r="B3" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -834,7 +830,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586490</v>
+        <v>586387</v>
       </c>
       <c r="R3" t="n">
-        <v>6931210</v>
+        <v>6931007</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -895,7 +895,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hundratals.</t>
+          <t>Flertalet knärötter, flera små på gång. I en grop.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123874759</v>
+        <v>123874739</v>
       </c>
       <c r="B4" t="n">
-        <v>98504</v>
+        <v>79869</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,31 +935,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -967,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586475</v>
+        <v>586451</v>
       </c>
       <c r="R4" t="n">
-        <v>6931222</v>
+        <v>6931253</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1013,6 +1012,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På avbruten sälg.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123874645</v>
+        <v>123874718</v>
       </c>
       <c r="B5" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1084,13 +1088,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586409</v>
+        <v>586339</v>
       </c>
       <c r="R5" t="n">
-        <v>6931021</v>
+        <v>6931134</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,7 +1138,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På liten kulle nära stor asp.</t>
+          <t>I slänten ner mot fuktig mark.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,10 +1166,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123874718</v>
+        <v>123874759</v>
       </c>
       <c r="B6" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1206,10 +1210,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586339</v>
+        <v>586475</v>
       </c>
       <c r="R6" t="n">
-        <v>6931134</v>
+        <v>6931222</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1252,11 +1256,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>I slänten ner mot fuktig mark.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,10 +1283,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123874739</v>
+        <v>123874788</v>
       </c>
       <c r="B7" t="n">
-        <v>79869</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1296,30 +1295,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586451</v>
+        <v>586490</v>
       </c>
       <c r="R7" t="n">
-        <v>6931253</v>
+        <v>6931210</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På avbruten sälg.</t>
+          <t>Hundratals.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1405,10 +1405,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123874615</v>
+        <v>123874676</v>
       </c>
       <c r="B8" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1417,30 +1417,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1448,13 +1449,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586434</v>
+        <v>586387</v>
       </c>
       <c r="R8" t="n">
-        <v>6931019</v>
+        <v>6931018</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1498,7 +1499,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Granlåga, rotvälta.</t>
+          <t>Vid granlåga.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1526,10 +1527,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123874676</v>
+        <v>123874615</v>
       </c>
       <c r="B9" t="n">
-        <v>98504</v>
+        <v>90990</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1538,31 +1539,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1570,13 +1570,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586387</v>
+        <v>586434</v>
       </c>
       <c r="R9" t="n">
-        <v>6931018</v>
+        <v>6931019</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Vid granlåga.</t>
+          <t>Granlåga, rotvälta.</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 12894-2025 artfynd.xlsx
+++ b/artfynd/A 12894-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123874645</v>
+        <v>123874718</v>
       </c>
       <c r="B2" t="n">
         <v>98079</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586409</v>
+        <v>586339</v>
       </c>
       <c r="R2" t="n">
-        <v>6931021</v>
+        <v>6931134</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -769,7 +769,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På liten kulle nära stor asp.</t>
+          <t>I slänten ner mot fuktig mark.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123874704</v>
+        <v>123874645</v>
       </c>
       <c r="B3" t="n">
         <v>98079</v>
@@ -830,11 +830,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -845,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586387</v>
+        <v>586409</v>
       </c>
       <c r="R3" t="n">
-        <v>6931007</v>
+        <v>6931021</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,7 +891,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Flertalet knärötter, flera små på gång. I en grop.</t>
+          <t>På liten kulle nära stor asp.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123874739</v>
+        <v>123874676</v>
       </c>
       <c r="B4" t="n">
-        <v>79869</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,30 +931,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -966,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586451</v>
+        <v>586387</v>
       </c>
       <c r="R4" t="n">
-        <v>6931253</v>
+        <v>6931018</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1016,7 +1013,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På avbruten sälg.</t>
+          <t>Vid granlåga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123874718</v>
+        <v>123874739</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
+        <v>79869</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,31 +1053,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1088,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586339</v>
+        <v>586451</v>
       </c>
       <c r="R5" t="n">
-        <v>6931134</v>
+        <v>6931253</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1138,7 +1134,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>I slänten ner mot fuktig mark.</t>
+          <t>På avbruten sälg.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1283,7 +1279,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123874788</v>
+        <v>123874704</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1316,7 +1312,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586490</v>
+        <v>586387</v>
       </c>
       <c r="R7" t="n">
-        <v>6931210</v>
+        <v>6931007</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Hundratals.</t>
+          <t>Flertalet knärötter, flera små på gång. I en grop.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1405,10 +1405,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123874676</v>
+        <v>123874615</v>
       </c>
       <c r="B8" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1417,31 +1417,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1449,13 +1448,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586387</v>
+        <v>586434</v>
       </c>
       <c r="R8" t="n">
-        <v>6931018</v>
+        <v>6931019</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1499,7 +1498,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Vid granlåga.</t>
+          <t>Granlåga, rotvälta.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1527,10 +1526,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123874615</v>
+        <v>123874788</v>
       </c>
       <c r="B9" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1539,30 +1538,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1570,13 +1570,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586434</v>
+        <v>586490</v>
       </c>
       <c r="R9" t="n">
-        <v>6931019</v>
+        <v>6931210</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Granlåga, rotvälta.</t>
+          <t>Hundratals.</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 12894-2025 artfynd.xlsx
+++ b/artfynd/A 12894-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123874718</v>
+        <v>123874739</v>
       </c>
       <c r="B2" t="n">
-        <v>98079</v>
+        <v>79869</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586339</v>
+        <v>586451</v>
       </c>
       <c r="R2" t="n">
-        <v>6931134</v>
+        <v>6931253</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -769,7 +768,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I slänten ner mot fuktig mark.</t>
+          <t>På avbruten sälg.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123874645</v>
+        <v>123874676</v>
       </c>
       <c r="B3" t="n">
         <v>98079</v>
@@ -841,13 +840,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586409</v>
+        <v>586387</v>
       </c>
       <c r="R3" t="n">
-        <v>6931021</v>
+        <v>6931018</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -891,7 +890,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På liten kulle nära stor asp.</t>
+          <t>Vid granlåga.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +918,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123874676</v>
+        <v>123874788</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -963,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586387</v>
+        <v>586490</v>
       </c>
       <c r="R4" t="n">
-        <v>6931018</v>
+        <v>6931210</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1013,7 +1012,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Vid granlåga.</t>
+          <t>Hundratals.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123874739</v>
+        <v>123874718</v>
       </c>
       <c r="B5" t="n">
-        <v>79869</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,30 +1052,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586451</v>
+        <v>586339</v>
       </c>
       <c r="R5" t="n">
-        <v>6931253</v>
+        <v>6931134</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På avbruten sälg.</t>
+          <t>I slänten ner mot fuktig mark.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123874759</v>
+        <v>123874615</v>
       </c>
       <c r="B6" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,31 +1174,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1206,13 +1205,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586475</v>
+        <v>586434</v>
       </c>
       <c r="R6" t="n">
-        <v>6931222</v>
+        <v>6931019</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1252,6 +1251,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Granlåga, rotvälta.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,7 +1283,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123874704</v>
+        <v>123874645</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1312,11 +1316,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586387</v>
+        <v>586409</v>
       </c>
       <c r="R7" t="n">
-        <v>6931007</v>
+        <v>6931021</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Flertalet knärötter, flera små på gång. I en grop.</t>
+          <t>På liten kulle nära stor asp.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1405,10 +1405,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123874615</v>
+        <v>123874704</v>
       </c>
       <c r="B8" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1417,30 +1417,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1448,13 +1453,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586434</v>
+        <v>586387</v>
       </c>
       <c r="R8" t="n">
-        <v>6931019</v>
+        <v>6931007</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1498,7 +1503,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Granlåga, rotvälta.</t>
+          <t>Flertalet knärötter, flera små på gång. I en grop.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1526,7 +1531,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123874788</v>
+        <v>123874759</v>
       </c>
       <c r="B9" t="n">
         <v>98079</v>
@@ -1570,10 +1575,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586490</v>
+        <v>586475</v>
       </c>
       <c r="R9" t="n">
-        <v>6931210</v>
+        <v>6931222</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1616,11 +1621,6 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hundratals.</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 12894-2025 artfynd.xlsx
+++ b/artfynd/A 12894-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123874739</v>
+        <v>123874704</v>
       </c>
       <c r="B2" t="n">
-        <v>79869</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586451</v>
+        <v>586387</v>
       </c>
       <c r="R2" t="n">
-        <v>6931253</v>
+        <v>6931007</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -768,7 +773,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På avbruten sälg.</t>
+          <t>Flertalet knärötter, flera små på gång. I en grop.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123874676</v>
+        <v>123874615</v>
       </c>
       <c r="B3" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,31 +813,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,13 +844,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586387</v>
+        <v>586434</v>
       </c>
       <c r="R3" t="n">
-        <v>6931018</v>
+        <v>6931019</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,7 +894,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Vid granlåga.</t>
+          <t>Granlåga, rotvälta.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,7 +922,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123874788</v>
+        <v>123874676</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -962,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586490</v>
+        <v>586387</v>
       </c>
       <c r="R4" t="n">
-        <v>6931210</v>
+        <v>6931018</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1012,7 +1016,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Hundratals.</t>
+          <t>Vid granlåga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,7 +1044,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123874718</v>
+        <v>123874759</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1084,10 +1088,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586339</v>
+        <v>586475</v>
       </c>
       <c r="R5" t="n">
-        <v>6931134</v>
+        <v>6931222</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1130,11 +1134,6 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>I slänten ner mot fuktig mark.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,10 +1161,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123874615</v>
+        <v>123874718</v>
       </c>
       <c r="B6" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,30 +1173,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586434</v>
+        <v>586339</v>
       </c>
       <c r="R6" t="n">
-        <v>6931019</v>
+        <v>6931134</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Granlåga, rotvälta.</t>
+          <t>I slänten ner mot fuktig mark.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1405,10 +1405,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123874704</v>
+        <v>123874739</v>
       </c>
       <c r="B8" t="n">
-        <v>98079</v>
+        <v>79869</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1417,35 +1417,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1453,10 +1448,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586387</v>
+        <v>586451</v>
       </c>
       <c r="R8" t="n">
-        <v>6931007</v>
+        <v>6931253</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1503,7 +1498,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Flertalet knärötter, flera små på gång. I en grop.</t>
+          <t>På avbruten sälg.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1531,7 +1526,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123874759</v>
+        <v>123874788</v>
       </c>
       <c r="B9" t="n">
         <v>98079</v>
@@ -1575,10 +1570,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586475</v>
+        <v>586490</v>
       </c>
       <c r="R9" t="n">
-        <v>6931222</v>
+        <v>6931210</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1621,6 +1616,11 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hundratals.</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 12894-2025 artfynd.xlsx
+++ b/artfynd/A 12894-2025 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123874615</v>
+        <v>123874718</v>
       </c>
       <c r="B3" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,30 +813,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -844,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586434</v>
+        <v>586339</v>
       </c>
       <c r="R3" t="n">
-        <v>6931019</v>
+        <v>6931134</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -894,7 +895,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Granlåga, rotvälta.</t>
+          <t>I slänten ner mot fuktig mark.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,7 +923,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123874676</v>
+        <v>123874788</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -966,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586387</v>
+        <v>586490</v>
       </c>
       <c r="R4" t="n">
-        <v>6931018</v>
+        <v>6931210</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1016,7 +1017,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Vid granlåga.</t>
+          <t>Hundratals.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123874759</v>
+        <v>123874615</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,31 +1057,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1088,13 +1088,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586475</v>
+        <v>586434</v>
       </c>
       <c r="R5" t="n">
-        <v>6931222</v>
+        <v>6931019</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,6 +1134,11 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Granlåga, rotvälta.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,10 +1166,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123874718</v>
+        <v>123874739</v>
       </c>
       <c r="B6" t="n">
-        <v>98079</v>
+        <v>79869</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,31 +1178,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1205,10 +1209,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586339</v>
+        <v>586451</v>
       </c>
       <c r="R6" t="n">
-        <v>6931134</v>
+        <v>6931253</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1255,7 +1259,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>I slänten ner mot fuktig mark.</t>
+          <t>På avbruten sälg.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1405,10 +1409,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123874739</v>
+        <v>123874759</v>
       </c>
       <c r="B8" t="n">
-        <v>79869</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1417,30 +1421,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1448,10 +1453,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586451</v>
+        <v>586475</v>
       </c>
       <c r="R8" t="n">
-        <v>6931253</v>
+        <v>6931222</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1494,11 +1499,6 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På avbruten sälg.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1526,7 +1526,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123874788</v>
+        <v>123874676</v>
       </c>
       <c r="B9" t="n">
         <v>98079</v>
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586490</v>
+        <v>586387</v>
       </c>
       <c r="R9" t="n">
-        <v>6931210</v>
+        <v>6931018</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Hundratals.</t>
+          <t>Vid granlåga.</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 12894-2025 artfynd.xlsx
+++ b/artfynd/A 12894-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123874739</v>
+        <v>123874676</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586451</v>
+        <v>586387</v>
       </c>
       <c r="R2" t="n">
-        <v>6931253</v>
+        <v>6931018</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -768,7 +769,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På avbruten sälg.</t>
+          <t>Vid granlåga.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123874615</v>
+        <v>123874739</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,21 +813,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -839,13 +840,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586434</v>
+        <v>586451</v>
       </c>
       <c r="R3" t="n">
-        <v>6931019</v>
+        <v>6931253</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,7 +890,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Granlåga, rotvälta.</t>
+          <t>På avbruten sälg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,7 +918,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123874759</v>
+        <v>123874718</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -961,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586475</v>
+        <v>586339</v>
       </c>
       <c r="R4" t="n">
-        <v>6931222</v>
+        <v>6931134</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1007,6 +1008,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>I slänten ner mot fuktig mark.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,7 +1040,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123874718</v>
+        <v>123874704</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1067,7 +1073,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1078,10 +1088,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586339</v>
+        <v>586387</v>
       </c>
       <c r="R5" t="n">
-        <v>6931134</v>
+        <v>6931007</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1128,7 +1138,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>I slänten ner mot fuktig mark.</t>
+          <t>Flertalet knärötter, flera små på gång. I en grop.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,7 +1166,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123874645</v>
+        <v>123874759</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1200,13 +1210,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586409</v>
+        <v>586475</v>
       </c>
       <c r="R6" t="n">
-        <v>6931021</v>
+        <v>6931222</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1246,11 +1256,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På liten kulle nära stor asp.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,10 +1283,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123874788</v>
+        <v>123874615</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,31 +1295,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1322,13 +1326,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586490</v>
+        <v>586434</v>
       </c>
       <c r="R7" t="n">
-        <v>6931210</v>
+        <v>6931019</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1372,7 +1376,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Hundratals.</t>
+          <t>Granlåga, rotvälta.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1400,7 +1404,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123874676</v>
+        <v>123874645</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1444,13 +1448,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586387</v>
+        <v>586409</v>
       </c>
       <c r="R8" t="n">
-        <v>6931018</v>
+        <v>6931021</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1494,7 +1498,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Vid granlåga.</t>
+          <t>På liten kulle nära stor asp.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1522,7 +1526,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123874704</v>
+        <v>123874788</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1555,11 +1559,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586387</v>
+        <v>586490</v>
       </c>
       <c r="R9" t="n">
-        <v>6931007</v>
+        <v>6931210</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Flertalet knärötter, flera små på gång. I en grop.</t>
+          <t>Hundratals.</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 12894-2025 artfynd.xlsx
+++ b/artfynd/A 12894-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123874676</v>
+        <v>123874759</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586387</v>
+        <v>586475</v>
       </c>
       <c r="R2" t="n">
-        <v>6931018</v>
+        <v>6931222</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -765,11 +765,6 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Vid granlåga.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123874739</v>
+        <v>123874676</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,30 +804,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586451</v>
+        <v>586387</v>
       </c>
       <c r="R3" t="n">
-        <v>6931253</v>
+        <v>6931018</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -890,7 +886,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På avbruten sälg.</t>
+          <t>Vid granlåga.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123874718</v>
+        <v>123874615</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,31 +926,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -962,13 +957,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586339</v>
+        <v>586434</v>
       </c>
       <c r="R4" t="n">
-        <v>6931134</v>
+        <v>6931019</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,7 +1007,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I slänten ner mot fuktig mark.</t>
+          <t>Granlåga, rotvälta.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1166,7 +1161,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123874759</v>
+        <v>123874788</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1210,10 +1205,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586475</v>
+        <v>586490</v>
       </c>
       <c r="R6" t="n">
-        <v>6931222</v>
+        <v>6931210</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1256,6 +1251,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hundratals.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1283,10 +1283,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123874615</v>
+        <v>123874645</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1295,30 +1295,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1326,10 +1327,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586434</v>
+        <v>586409</v>
       </c>
       <c r="R7" t="n">
-        <v>6931019</v>
+        <v>6931021</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1376,7 +1377,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Granlåga, rotvälta.</t>
+          <t>På liten kulle nära stor asp.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1404,10 +1405,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123874645</v>
+        <v>123874739</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1416,31 +1417,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1448,13 +1448,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586409</v>
+        <v>586451</v>
       </c>
       <c r="R8" t="n">
-        <v>6931021</v>
+        <v>6931253</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På liten kulle nära stor asp.</t>
+          <t>På avbruten sälg.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1526,7 +1526,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123874788</v>
+        <v>123874718</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586490</v>
+        <v>586339</v>
       </c>
       <c r="R9" t="n">
-        <v>6931210</v>
+        <v>6931134</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Hundratals.</t>
+          <t>I slänten ner mot fuktig mark.</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 12894-2025 artfynd.xlsx
+++ b/artfynd/A 12894-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123874759</v>
+        <v>123874704</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -708,7 +708,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -719,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586475</v>
+        <v>586387</v>
       </c>
       <c r="R2" t="n">
-        <v>6931222</v>
+        <v>6931007</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -765,6 +769,11 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flertalet knärötter, flera små på gång. I en grop.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123874676</v>
+        <v>123874645</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -836,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586387</v>
+        <v>586409</v>
       </c>
       <c r="R3" t="n">
-        <v>6931018</v>
+        <v>6931021</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,7 +895,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Vid granlåga.</t>
+          <t>På liten kulle nära stor asp.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1035,7 +1044,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123874704</v>
+        <v>123874676</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1068,11 +1077,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1086,7 +1091,7 @@
         <v>586387</v>
       </c>
       <c r="R5" t="n">
-        <v>6931007</v>
+        <v>6931018</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1133,7 +1138,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flertalet knärötter, flera små på gång. I en grop.</t>
+          <t>Vid granlåga.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,7 +1166,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123874788</v>
+        <v>123874718</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1205,10 +1210,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586490</v>
+        <v>586339</v>
       </c>
       <c r="R6" t="n">
-        <v>6931210</v>
+        <v>6931134</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1255,7 +1260,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Hundratals.</t>
+          <t>I slänten ner mot fuktig mark.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1283,7 +1288,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123874645</v>
+        <v>123874759</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1327,13 +1332,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586409</v>
+        <v>586475</v>
       </c>
       <c r="R7" t="n">
-        <v>6931021</v>
+        <v>6931222</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1373,11 +1378,6 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På liten kulle nära stor asp.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1405,10 +1405,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123874739</v>
+        <v>123874788</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1417,30 +1417,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1448,10 +1449,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586451</v>
+        <v>586490</v>
       </c>
       <c r="R8" t="n">
-        <v>6931253</v>
+        <v>6931210</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1498,7 +1499,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På avbruten sälg.</t>
+          <t>Hundratals.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1526,10 +1527,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123874718</v>
+        <v>123874739</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1538,31 +1539,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586339</v>
+        <v>586451</v>
       </c>
       <c r="R9" t="n">
-        <v>6931134</v>
+        <v>6931253</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I slänten ner mot fuktig mark.</t>
+          <t>På avbruten sälg.</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 12894-2025 artfynd.xlsx
+++ b/artfynd/A 12894-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123874704</v>
+        <v>123874718</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -708,11 +708,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -723,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586387</v>
+        <v>586339</v>
       </c>
       <c r="R2" t="n">
-        <v>6931007</v>
+        <v>6931134</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -773,7 +769,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Flertalet knärötter, flera små på gång. I en grop.</t>
+          <t>I slänten ner mot fuktig mark.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123874645</v>
+        <v>123874676</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -845,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586409</v>
+        <v>586387</v>
       </c>
       <c r="R3" t="n">
-        <v>6931021</v>
+        <v>6931018</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,7 +891,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På liten kulle nära stor asp.</t>
+          <t>Vid granlåga.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1044,7 +1040,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123874676</v>
+        <v>123874704</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1077,7 +1073,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1091,7 +1091,7 @@
         <v>586387</v>
       </c>
       <c r="R5" t="n">
-        <v>6931018</v>
+        <v>6931007</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Vid granlåga.</t>
+          <t>Flertalet knärötter, flera små på gång. I en grop.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,7 +1166,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123874718</v>
+        <v>123874645</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1210,13 +1210,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>586339</v>
+        <v>586409</v>
       </c>
       <c r="R6" t="n">
-        <v>6931134</v>
+        <v>6931021</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>I slänten ner mot fuktig mark.</t>
+          <t>På liten kulle nära stor asp.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,7 +1288,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123874759</v>
+        <v>123874788</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586475</v>
+        <v>586490</v>
       </c>
       <c r="R7" t="n">
-        <v>6931222</v>
+        <v>6931210</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1378,6 +1378,11 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hundratals.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1405,7 +1410,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123874788</v>
+        <v>123874759</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1449,10 +1454,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586490</v>
+        <v>586475</v>
       </c>
       <c r="R8" t="n">
-        <v>6931210</v>
+        <v>6931222</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1495,11 +1500,6 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hundratals.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 12894-2025 artfynd.xlsx
+++ b/artfynd/A 12894-2025 artfynd.xlsx
@@ -1648,10 +1648,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126836148</v>
+        <v>126836899</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1659,34 +1659,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hammarsjökuttan, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586382</v>
+        <v>586338</v>
       </c>
       <c r="R10" t="n">
-        <v>6931176</v>
+        <v>6931140</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1719,6 +1724,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1745,10 +1755,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126836899</v>
+        <v>126836148</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>79011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,39 +1766,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hammarsjökuttan, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586338</v>
+        <v>586382</v>
       </c>
       <c r="R11" t="n">
-        <v>6931140</v>
+        <v>6931176</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1821,11 +1826,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1855,7 +1855,7 @@
         <v>126835458</v>
       </c>
       <c r="B12" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126835956</v>
+        <v>126836030</v>
       </c>
       <c r="B16" t="n">
         <v>57657</v>

--- a/artfynd/A 12894-2025 artfynd.xlsx
+++ b/artfynd/A 12894-2025 artfynd.xlsx
@@ -1758,7 +1758,7 @@
         <v>126836148</v>
       </c>
       <c r="B11" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>126835458</v>
       </c>
       <c r="B12" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 12894-2025 artfynd.xlsx
+++ b/artfynd/A 12894-2025 artfynd.xlsx
@@ -1648,10 +1648,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126836899</v>
+        <v>126836148</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1659,39 +1659,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hammarsjökuttan, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586338</v>
+        <v>586382</v>
       </c>
       <c r="R10" t="n">
-        <v>6931140</v>
+        <v>6931176</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1724,11 +1719,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1755,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126836148</v>
+        <v>126836899</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,34 +1756,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hammarsjökuttan, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586382</v>
+        <v>586338</v>
       </c>
       <c r="R11" t="n">
-        <v>6931176</v>
+        <v>6931140</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1826,6 +1821,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 12894-2025 artfynd.xlsx
+++ b/artfynd/A 12894-2025 artfynd.xlsx
@@ -1852,10 +1852,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126835458</v>
+        <v>126836091</v>
       </c>
       <c r="B12" t="n">
-        <v>91325</v>
+        <v>58087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1863,34 +1863,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>103001</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hammarsjön, Mpd</t>
+          <t>Hammarsjökuttan, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586481</v>
+        <v>586398</v>
       </c>
       <c r="R12" t="n">
-        <v>6931249</v>
+        <v>6931194</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1949,10 +1954,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126836091</v>
+        <v>126835458</v>
       </c>
       <c r="B13" t="n">
-        <v>58087</v>
+        <v>91325</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1960,39 +1965,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103001</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hammarsjökuttan, Mpd</t>
+          <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>586398</v>
+        <v>586481</v>
       </c>
       <c r="R13" t="n">
-        <v>6931194</v>
+        <v>6931249</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2265,7 +2265,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126836030</v>
+        <v>126835956</v>
       </c>
       <c r="B16" t="n">
         <v>57657</v>

--- a/artfynd/A 12894-2025 artfynd.xlsx
+++ b/artfynd/A 12894-2025 artfynd.xlsx
@@ -1957,7 +1957,7 @@
         <v>126835458</v>
       </c>
       <c r="B13" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126835956</v>
+        <v>126836030</v>
       </c>
       <c r="B16" t="n">
         <v>57657</v>

--- a/artfynd/A 12894-2025 artfynd.xlsx
+++ b/artfynd/A 12894-2025 artfynd.xlsx
@@ -1648,10 +1648,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126836148</v>
+        <v>126836899</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1659,34 +1659,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hammarsjökuttan, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586382</v>
+        <v>586338</v>
       </c>
       <c r="R10" t="n">
-        <v>6931176</v>
+        <v>6931140</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1719,6 +1724,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1745,10 +1755,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126836899</v>
+        <v>126836148</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,39 +1766,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hammarsjökuttan, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586338</v>
+        <v>586382</v>
       </c>
       <c r="R11" t="n">
-        <v>6931140</v>
+        <v>6931176</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1821,11 +1826,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126836091</v>
+        <v>126835458</v>
       </c>
       <c r="B12" t="n">
-        <v>58087</v>
+        <v>91326</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1863,39 +1863,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103001</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hammarsjökuttan, Mpd</t>
+          <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586398</v>
+        <v>586481</v>
       </c>
       <c r="R12" t="n">
-        <v>6931194</v>
+        <v>6931249</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1954,10 +1949,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126835458</v>
+        <v>126836091</v>
       </c>
       <c r="B13" t="n">
-        <v>91326</v>
+        <v>58087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1965,34 +1960,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>103001</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hammarsjön, Mpd</t>
+          <t>Hammarsjökuttan, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>586481</v>
+        <v>586398</v>
       </c>
       <c r="R13" t="n">
-        <v>6931249</v>
+        <v>6931194</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 12894-2025 artfynd.xlsx
+++ b/artfynd/A 12894-2025 artfynd.xlsx
@@ -1648,10 +1648,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126836899</v>
+        <v>126836148</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1659,39 +1659,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hammarsjökuttan, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586338</v>
+        <v>586382</v>
       </c>
       <c r="R10" t="n">
-        <v>6931140</v>
+        <v>6931176</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1724,11 +1719,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1755,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126836148</v>
+        <v>126836899</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>57661</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,34 +1756,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hammarsjökuttan, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586382</v>
+        <v>586338</v>
       </c>
       <c r="R11" t="n">
-        <v>6931176</v>
+        <v>6931140</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1826,6 +1821,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1855,7 +1855,7 @@
         <v>126835458</v>
       </c>
       <c r="B12" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>126836091</v>
       </c>
       <c r="B13" t="n">
-        <v>58087</v>
+        <v>58091</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>126837365</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>126835570</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126836030</v>
+        <v>126835956</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>126837105</v>
       </c>
       <c r="B17" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>126837147</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>126836809</v>
       </c>
       <c r="B19" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>126837188</v>
       </c>
       <c r="B20" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>126837260</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126835600</v>
+        <v>126836133</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2943,14 +2943,14 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hammarsjön, Mpd</t>
+          <t>Hammarsjökuttan, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586470</v>
+        <v>586382</v>
       </c>
       <c r="R22" t="n">
-        <v>6931233</v>
+        <v>6931176</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3014,10 +3014,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126836133</v>
+        <v>126835600</v>
       </c>
       <c r="B23" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3050,14 +3050,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hammarsjökuttan, Mpd</t>
+          <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586382</v>
+        <v>586470</v>
       </c>
       <c r="R23" t="n">
-        <v>6931176</v>
+        <v>6931233</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3124,7 +3124,7 @@
         <v>126836188</v>
       </c>
       <c r="B24" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 12894-2025 artfynd.xlsx
+++ b/artfynd/A 12894-2025 artfynd.xlsx
@@ -1648,10 +1648,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126836148</v>
+        <v>126836899</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1659,34 +1659,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hammarsjökuttan, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586382</v>
+        <v>586338</v>
       </c>
       <c r="R10" t="n">
-        <v>6931176</v>
+        <v>6931140</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1719,6 +1724,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1745,10 +1755,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126836899</v>
+        <v>126836148</v>
       </c>
       <c r="B11" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,39 +1766,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hammarsjökuttan, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586338</v>
+        <v>586382</v>
       </c>
       <c r="R11" t="n">
-        <v>6931140</v>
+        <v>6931176</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1821,11 +1826,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2265,7 +2265,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126835956</v>
+        <v>126836030</v>
       </c>
       <c r="B16" t="n">
         <v>57661</v>
@@ -2907,7 +2907,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126836133</v>
+        <v>126835600</v>
       </c>
       <c r="B22" t="n">
         <v>57661</v>
@@ -2943,14 +2943,14 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hammarsjökuttan, Mpd</t>
+          <t>Hammarsjön, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586382</v>
+        <v>586470</v>
       </c>
       <c r="R22" t="n">
-        <v>6931176</v>
+        <v>6931233</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3014,7 +3014,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126835600</v>
+        <v>126836133</v>
       </c>
       <c r="B23" t="n">
         <v>57661</v>
@@ -3050,14 +3050,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hammarsjön, Mpd</t>
+          <t>Hammarsjökuttan, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586470</v>
+        <v>586382</v>
       </c>
       <c r="R23" t="n">
-        <v>6931233</v>
+        <v>6931176</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
